--- a/ig/DM-JUIN-2025/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
+++ b/ig/DM-JUIN-2025/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="577">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250425120000</t>
+    <t>20250625120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T12:00:00+01:00</t>
+    <t>2025-06-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1026,7 +1026,7 @@
     <t>157</t>
   </si>
   <si>
-    <t>Unité hospitalière de gynécologie</t>
+    <t>Unité hospitalière de gynécologie et/ou obstétrique</t>
   </si>
   <si>
     <t>158</t>
@@ -1248,7 +1248,7 @@
     <t>194</t>
   </si>
   <si>
-    <t>Cabinet de ville de gynécologie</t>
+    <t>Cabinet de ville de gynécologie et/ou obstétrique</t>
   </si>
   <si>
     <t>195</t>
@@ -1500,7 +1500,7 @@
     <t>236</t>
   </si>
   <si>
-    <t>Unité hospitalière d'orthopédie dento-faciale (odontologie)</t>
+    <t>Unité hospitalière d'odontologie</t>
   </si>
   <si>
     <t>237</t>
@@ -1687,6 +1687,54 @@
   </si>
   <si>
     <t>Equipe mobile d'endocrinologie, diabétologie, métabolisme et nutrition</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>Centre de lutte antituberculeuse (CLAT)</t>
+  </si>
+  <si>
+    <t>269</t>
+  </si>
+  <si>
+    <t>Centre de vaccination</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>Centre de vaccination internationale</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>Dialyse à Domicile</t>
+  </si>
+  <si>
+    <t>272</t>
+  </si>
+  <si>
+    <t>Equipe de Liaison et de Soins en Addictologie (ELSA)</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>Unité d’auto-dialyse assistée (UAD)</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>Unité de dialyse en centre lourd</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>Unité de dialyse Médicalisée (UDM)</t>
   </si>
   <si>
     <t/>
@@ -1957,7 +2005,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B268"/>
+  <dimension ref="A1:B276"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4097,15 +4145,79 @@
         <v>558</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B269" t="s" s="2">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B270" t="s" s="2">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B271" t="s" s="2">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="B272" t="s" s="2">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B273" t="s" s="2">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="B274" t="s" s="2">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="B275" t="s" s="2">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B276" t="s" s="2">
+        <v>576</v>
       </c>
     </row>
   </sheetData>
